--- a/data/trans_bre/P1402-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1402-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,38</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-3,01%</t>
+          <t>-3,81%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,42</t>
+          <t>-2,33; 2,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 3,01</t>
+          <t>-2,42; 2,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,84</t>
+          <t>-4,85; 1,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 2,3</t>
+          <t>-3,29; 2,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,85; 51,97</t>
+          <t>-33,36; 60,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,84; 53,09</t>
+          <t>-29,34; 55,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,16; 23,73</t>
+          <t>-42,94; 21,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 27,7</t>
+          <t>-27,23; 25,5</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>-9,92%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,68</t>
+          <t>-1,09; 3,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 4,02</t>
+          <t>-0,7; 3,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,28</t>
+          <t>-2,68; 2,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 4,74</t>
+          <t>-3,0; 1,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 64,53</t>
+          <t>-13,71; 65,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 72,4</t>
+          <t>-10,44; 69,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 31,18</t>
+          <t>-29,18; 32,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 121,39</t>
+          <t>-30,35; 15,26</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,04</t>
+          <t>-2,46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-44,85%</t>
+          <t>-27,75%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,81</t>
+          <t>0,01; 4,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 4,3</t>
+          <t>-1,66; 4,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,96</t>
+          <t>-3,9; 2,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,74; -1,39</t>
+          <t>-5,18; -0,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 141,19</t>
+          <t>-1,09; 144,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 74,19</t>
+          <t>-18,84; 68,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-35,87; 25,84</t>
+          <t>-34,92; 27,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-73,7; -18,91</t>
+          <t>-48,72; -3,31</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,82</t>
+          <t>-2,15</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-29,23%</t>
+          <t>-22,31%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,09</t>
+          <t>-1,01; 2,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,79</t>
+          <t>-1,58; 3,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,27</t>
+          <t>-1,91; 3,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,03; -0,71</t>
+          <t>-4,08; -0,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 69,63</t>
+          <t>-17,51; 67,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 47,14</t>
+          <t>-14,91; 51,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 47,24</t>
+          <t>-20,89; 47,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,92; -9,07</t>
+          <t>-38,49; -0,18</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-16,94%</t>
+          <t>-15,99%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,3</t>
+          <t>-0,02; 2,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,63</t>
+          <t>-0,2; 2,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,06</t>
+          <t>-1,69; 1,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,49</t>
+          <t>-2,73; -0,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 43,93</t>
+          <t>-0,66; 42,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 38,0</t>
+          <t>-2,31; 36,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 13,26</t>
+          <t>-18,16; 16,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,61; 4,79</t>
+          <t>-26,92; -4,57</t>
         </is>
       </c>
     </row>
